--- a/Trans To Vostok/Template/Texture.xlsx
+++ b/Trans To Vostok/Template/Texture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Trans To Vostok\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC68A55-7B5A-4DEF-85F9-C7BB8DCB6F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFEB27D-9773-4B27-86A6-264570BFBDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E0CAA4CC-5EC0-4298-9780-F39DB2CE6684}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
   <si>
     <t>Tutorial</t>
   </si>
@@ -999,9 +999,6 @@
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="J2" s="5" t="s">
         <v>66</v>
       </c>
@@ -1026,9 +1023,6 @@
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="4" spans="1:10" ht="261">
       <c r="A4" s="1" t="s">
@@ -1050,9 +1044,6 @@
       <c r="G4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="5" spans="1:10" ht="243.6">
       <c r="A5" s="1" t="s">
@@ -1074,9 +1065,6 @@
       <c r="G5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="6" spans="1:10" ht="261">
       <c r="A6" s="1" t="s">
@@ -1098,9 +1086,6 @@
       <c r="G6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="7" spans="1:10" ht="278.39999999999998">
       <c r="A7" s="1" t="s">
@@ -1122,9 +1107,6 @@
       <c r="G7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="8" spans="1:10" ht="313.2">
       <c r="A8" s="1" t="s">
@@ -1146,9 +1128,6 @@
       <c r="G8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="9" spans="1:10" ht="261">
       <c r="A9" s="1" t="s">
@@ -1170,9 +1149,6 @@
       <c r="G9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="10" spans="1:10" ht="261">
       <c r="A10" s="1" t="s">
@@ -1194,9 +1170,6 @@
       <c r="G10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="11" spans="1:10" ht="400.2">
       <c r="A11" s="1" t="s">
@@ -1218,9 +1191,6 @@
       <c r="G11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="12" spans="1:10" ht="261">
       <c r="A12" s="1" t="s">
@@ -1242,9 +1212,6 @@
       <c r="G12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="13" spans="1:10" ht="243.6">
       <c r="A13" s="1" t="s">
@@ -1266,9 +1233,6 @@
       <c r="G13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="14" spans="1:10" ht="261">
       <c r="A14" s="2" t="s">
@@ -1290,9 +1254,6 @@
       <c r="G14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="15" spans="1:10" ht="278.39999999999998">
       <c r="A15" s="2" t="s">
@@ -1314,9 +1275,6 @@
       <c r="G15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="16" spans="1:10" ht="243.6">
       <c r="A16" s="2" t="s">
@@ -1338,9 +1296,6 @@
       <c r="G16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="17" spans="1:10" ht="261">
       <c r="A17" s="2" t="s">
@@ -1361,9 +1316,6 @@
       </c>
       <c r="G17" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>65</v>
